--- a/dados/excel/genero_por_categoria.xlsx
+++ b/dados/excel/genero_por_categoria.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
@@ -886,22 +886,22 @@
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>5331</v>
+        <v>5455</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>80295364.32000001</v>
+        <v>82258231.34</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>15061.97042205965</v>
+        <v>15079.41912740605</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="H2" s="12" t="n">
-        <v>36.42</v>
+        <v>36.07</v>
       </c>
     </row>
     <row r="3">
@@ -916,22 +916,22 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3385</v>
+        <v>3460</v>
       </c>
       <c r="D3" s="14" t="n">
         <v>224</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>47133956.51</v>
+        <v>48289863.25</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>13924.35938257016</v>
+        <v>13956.60787572254</v>
       </c>
       <c r="G3" s="16" t="n">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="H3" s="17" t="n">
-        <v>36.42</v>
+        <v>36.07</v>
       </c>
     </row>
     <row r="4">
@@ -946,22 +946,22 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9" t="n">
         <v>9</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>1849827.35</v>
+        <v>1867276.81</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>14339.74689922481</v>
+        <v>14254.02145038168</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>36.42</v>
+        <v>36.07</v>
       </c>
     </row>
     <row r="5">
@@ -976,22 +976,22 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>471186</v>
+        <v>479186</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>10039</v>
+        <v>10149</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>3449561457.17</v>
+        <v>3527338956.9</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>7321.018572644349</v>
+        <v>7361.106035860814</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>13594</v>
+        <v>13740</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>73.84999999999999</v>
+        <v>73.86</v>
       </c>
     </row>
     <row r="6">
@@ -1006,22 +1006,22 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>152560</v>
+        <v>155305</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>3372</v>
+        <v>3404</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1402909898.55</v>
+        <v>1432945406.78</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>9195.791154627686</v>
+        <v>9226.653403174398</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>13594</v>
+        <v>13740</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>73.84999999999999</v>
+        <v>73.86</v>
       </c>
     </row>
     <row r="7">
@@ -1036,22 +1036,22 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>8888</v>
+        <v>9025</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>68499951.93000001</v>
+        <v>69834495.31999999</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>7707.015293654366</v>
+        <v>7737.894218282548</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>13594</v>
+        <v>13740</v>
       </c>
       <c r="H7" s="17" t="n">
-        <v>73.84999999999999</v>
+        <v>73.86</v>
       </c>
     </row>
     <row r="8">
@@ -1066,22 +1066,22 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>136764</v>
+        <v>139810</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>10069</v>
+        <v>10292</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>215219284.98</v>
+        <v>221420896.11</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1573.654506887777</v>
+        <v>1583.727173378156</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>11682</v>
+        <v>11925</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>86.19</v>
+        <v>86.31</v>
       </c>
     </row>
     <row r="9">
@@ -1096,22 +1096,22 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>15772</v>
+        <v>16051</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1500</v>
+        <v>1519</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>34830265.37</v>
+        <v>35257936.64</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>2208.360725970073</v>
+        <v>2196.619315930472</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>11682</v>
+        <v>11925</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>86.19</v>
+        <v>86.31</v>
       </c>
     </row>
     <row r="10">
@@ -1126,22 +1126,22 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1564</v>
+        <v>1595</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3474226.4</v>
+        <v>3547081.88</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2221.372378516624</v>
+        <v>2223.875786833856</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>11682</v>
+        <v>11925</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>86.19</v>
+        <v>86.31</v>
       </c>
     </row>
     <row r="11">
@@ -1156,22 +1156,22 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>25619</v>
+        <v>26028</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>296972513.69</v>
+        <v>303260106.29</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>11591.88546352317</v>
+        <v>11651.30268518519</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>63.35</v>
+        <v>63.41</v>
       </c>
     </row>
     <row r="12">
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>14037</v>
+        <v>14260</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>178256947.87</v>
+        <v>181707478.03</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>12699.07728645722</v>
+        <v>12742.45988990182</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>63.35</v>
+        <v>63.41</v>
       </c>
     </row>
     <row r="13">
@@ -1216,22 +1216,22 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>7887599.69</v>
+        <v>8061006.24</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>16746.49615711253</v>
+        <v>16828.8230480167</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>63.35</v>
+        <v>63.41</v>
       </c>
     </row>
     <row r="14">
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>10686</v>
+        <v>10816</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>205</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>45762427.09</v>
+        <v>46491210.45</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>4282.465570840352</v>
+        <v>4298.373747226332</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>298</v>
@@ -1276,16 +1276,16 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>3923</v>
+        <v>3967</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>89</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>22730513.22</v>
+        <v>23054936.52</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>5794.166000509814</v>
+        <v>5811.680494076128</v>
       </c>
       <c r="G15" s="16" t="n">
         <v>298</v>
@@ -1306,16 +1306,16 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>4</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1272269.57</v>
+        <v>1292840.97</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>6298.364207920792</v>
+        <v>6337.455735294117</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>298</v>
